--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2022_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:42</t>
+    <t xml:space="preserve">2026-09-24 01:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -739,7 +739,7 @@
         <v>0.16</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.2</v>
@@ -762,7 +762,7 @@
         <v>0.09</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.04</v>
@@ -785,7 +785,7 @@
         <v>0.12</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.2</v>
@@ -805,13 +805,13 @@
         <v>19</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="14">
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.2</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.21</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>334</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="16">
@@ -868,19 +868,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>334</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.24</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>19</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.18</v>
+        <v>0.3</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>334</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2022_nuble.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:32</t>
+    <t xml:space="preserve">2026-10-01 23:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2022_nuble.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2022_nuble.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:19</t>
+    <t xml:space="preserve">2026-10-05 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
